--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Rupak Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9849498091</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9849498091</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9849498091</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9849498091</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.69411</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.69411</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -930,10 +924,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH2" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="inlineStr"/>
       <c r="AJ2" s="3" t="inlineStr"/>
@@ -948,25 +940,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>CDB236</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.26801</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.26801</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -978,6 +978,436 @@
         </is>
       </c>
       <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 1:00 PM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>No internet connection</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376190</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Shrestha</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Shrestha</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9849498091</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:56:39 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9849498091</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:27:02 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:00:24 PM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.69411</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu,Naikap, khadkagaun,Near LRI School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>srupak809@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>08:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB236</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.26801</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>22h 3m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>No internet connection</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376190</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Shrestha</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Shrestha</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9849498091</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:56:39 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9849498091</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:27:02 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:00:24 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.69411</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu,Naikap, khadkagaun,Near LRI School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>srupak809@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>08:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB236</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.26801</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>22h 3m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -994,20 +1424,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1031,7 +1461,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1041,7 +1471,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1052,7 +1482,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1494,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>22h 3m</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1506,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
@@ -1117,14 +1547,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1605,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1258,6 +1688,140 @@
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376190</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Shrestha</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:56:39 PM</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:27:02 PM</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:00:24 PM</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>22h 3m</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TKT1376190</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Rupak Shrestha</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:56:39 PM</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:27:02 PM</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:00:24 PM</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>22h 3m</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -483,12 +483,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -497,7 +497,7 @@
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -517,14 +517,14 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -1050,10 +1050,8 @@
           <t>Rupak Shrestha</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9849498091</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9849498091</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1068,10 +1066,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9849498091</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9849498091</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1088,10 +1084,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.69411</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.69411</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1129,10 +1123,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH3" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
@@ -1151,25 +1143,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>CDB236</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.26801</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.26801</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1265,10 +1253,8 @@
           <t>Rupak Shrestha</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9849498091</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9849498091</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1283,10 +1269,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9849498091</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9849498091</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1303,10 +1287,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.69411</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.69411</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1344,10 +1326,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH4" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
@@ -1366,50 +1346,452 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB236</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.26801</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.26801</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>22h 3m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>22h 3m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 1:03 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376517</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Binita sharma</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Binita sharma</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9746235375</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841151615</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 10:05:35 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>near by Paropakar Maternity &amp; Women's Hospital Kupondole branch - Hospital M8Q8+8Q3 Lalitpur 44600,</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>prasamshapoudelna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>02:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2h 58m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 1:02 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV remote</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376513</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PRAMOD YADAV</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>PRAMOD YADAV</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9851202417</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:02:37 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851202417</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 10:02:39 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:02:37 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Bodhigram Lalitpur 44700, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>PRAMODYADAV55523@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>03:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB574</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2h 59m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1432,7 +1814,7 @@
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
@@ -1461,7 +1843,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1471,7 +1853,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1482,7 +1864,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1876,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22h 3m</t>
+          <t>11h 1m</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1888,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 33m</t>
+          <t>12h 46m</t>
         </is>
       </c>
     </row>
@@ -1543,285 +1925,483 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1376190</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Rupak Shrestha</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:56:39 PM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:27:02 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:00:24 PM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>22h 3m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TKT1376190</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Rupak Shrestha</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>22 Oct 2026 02:56:39 PM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>22 Oct 2026 02:27:02 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>23 Oct 2026 01:00:24 PM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>22h 3m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>22h 33m</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TKT1376190</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Rupak Shrestha</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1376517</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Binita sharma</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 10:05:35 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>2h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376513</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>PRAMOD YADAV</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:56:39 PM</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:27:02 PM</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 01:00:24 PM</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>22h 3m</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:02:37 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 10:02:39 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:02:37 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>2h 59m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -524,7 +524,7 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1456,10 +1456,8 @@
           <t>Binita sharma</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9746235375</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9746235375</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1549,10 +1547,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1563,7 +1559,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1659,10 +1655,8 @@
           <t>PRAMOD YADAV</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9851202417</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9851202417</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1752,10 +1746,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -1766,32 +1758,454 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2h 59m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376351</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Purnaraj Maharjan</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Purnaraj Maharjan</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9840475969</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:37:47 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9840475969</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 08:02:19 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:37:47 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.71664</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Banasthali ward no:15,Chamati tole, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>rabingolden63@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>03:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.303</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>2h 59m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>17h 35m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376631</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9861569905</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:21:09 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9861569905</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:21:09 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:20:06 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.657741</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Unnamed Road, M958+5CJ, Mahalaxmi 44600, Near by Shree Jana Sneha Krishi Bahu Udesya Sahakari Sansth</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>rautnirajan306@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Khadka</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L27-6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.366226</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1815,7 +2229,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1843,7 +2257,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1864,7 +2278,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -1929,14 +2343,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2005,14 +2419,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2718,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2371,7 +2785,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1844,20 +1844,14 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Purnaraj Maharjan</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9840475969</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9840475969</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1892,10 +1886,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.71664</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.71664</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1933,10 +1925,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH7" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
@@ -1955,25 +1945,21 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.303</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.303</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2069,10 +2055,8 @@
           <t>Nirajan Raut</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9861569905</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9861569905</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2107,10 +2091,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.657741</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.657741</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2162,50 +2144,249 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L27-6</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.366226</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.366226</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>58m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>58m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 1:44 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>iptv stb box</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376271</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra Moktan Tamang</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra Moktan Tamang</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9801062656</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:44:00 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851062656</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 04:47:06 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:44:00 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>27.655114, 85.430721 - Suryabinayak Municipality, Bhaktapur, Bagmati, Nepal, Nepal, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>06:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L44-1</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>20h 56m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2229,7 +2410,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2257,7 +2438,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2267,7 +2448,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2278,7 +2459,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2471,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 1m</t>
+          <t>8h 49m</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2483,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>12h 46m</t>
+          <t>14h 24m</t>
         </is>
       </c>
     </row>
@@ -2361,14 +2542,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2461,160 +2642,116 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1376190</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Rupak Shrestha</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:56:39 PM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:27:02 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 01:00:24 PM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>22h 3m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
         </is>
       </c>
     </row>
@@ -2688,32 +2825,32 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1376517</t>
+          <t>TKT1376190</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Binita sharma</t>
+          <t>Rupak Shrestha</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2723,99 +2860,233 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 01:03:39 PM</t>
+          <t>22 Oct 2026 02:56:39 PM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 10:05:35 AM</t>
+          <t>22 Oct 2026 02:27:02 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 01:03:39 PM</t>
+          <t>23 Oct 2026 01:00:24 PM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 3m</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>2h 58m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>TKT1376517</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Binita sharma</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 10:05:35 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>2h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>TKT1376513</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>PRAMOD YADAV</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 01:02:37 PM</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 01:02:37 PM</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>2h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376271</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Dipendra Moktan Tamang</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:44:00 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 04:47:06 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:44:00 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>20h 56m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2254,10 +2254,8 @@
           <t>Dipendra Moktan Tamang</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9801062656</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9801062656</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2325,10 +2323,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2347,10 +2343,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2361,32 +2355,247 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>20h 56m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 2:01 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>slow inetrnt</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375830</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Prisha Maharjan</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Prisha Maharjan</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9767470067</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:01:16 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>LTP9767470067</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 08:25:06 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:01:16 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>27.636191101081145, 85.34222936782227, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>mlillyy0901@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>14:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>20h 56m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 36m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2438,7 +2647,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2448,7 +2657,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2459,7 +2668,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2680,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 49m</t>
+          <t>7h 21m</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2692,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>18h 56m</t>
         </is>
       </c>
     </row>
@@ -2553,84 +2762,79 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2846,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -2665,259 +2869,171 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1376190</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Rupak Shrestha</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:56:39 PM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:27:02 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 01:00:24 PM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>22h 3m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1376190</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Rupak Shrestha</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:56:39 PM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>22 Oct 2026 02:27:02 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 01:00:24 PM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>22h 3m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1376517</t>
+          <t>TKT1376190</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Binita sharma</t>
+          <t>Rupak Shrestha</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2927,44 +3043,44 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 01:03:39 PM</t>
+          <t>22 Oct 2026 02:56:39 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 10:05:35 AM</t>
+          <t>22 Oct 2026 02:27:02 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 01:03:39 PM</t>
+          <t>23 Oct 2026 01:00:24 PM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 3m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2h 58m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1376513</t>
+          <t>TKT1376190</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>PRAMOD YADAV</t>
+          <t>Rupak Shrestha</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2974,17 +3090,17 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2994,99 +3110,300 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+          <t>Case : No internet connection   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 01:02:37 PM</t>
+          <t>22 Oct 2026 02:56:39 PM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 10:02:39 AM</t>
+          <t>22 Oct 2026 02:27:02 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 01:02:37 PM</t>
+          <t>23 Oct 2026 01:00:24 PM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 3m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>2h 59m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>TKT1376517</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Binita sharma</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 10:05:35 AM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:03:39 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>2h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1376513</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>PRAMOD YADAV</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:02:37 PM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 10:02:39 AM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:02:37 PM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>2h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>TKT1376271</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Dipendra Moktan Tamang</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv stb box   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>23 Oct 2026 01:44:00 PM</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>22 Oct 2026 04:47:06 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>23 Oct 2026 01:44:00 PM</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>20h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1375830</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Prisha Maharjan</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:01:16 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 08:25:06 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:01:16 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 17h 36m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2451,10 +2451,8 @@
           <t>Prisha Maharjan</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9767470067</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9767470067</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2489,10 +2487,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2530,10 +2526,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
@@ -2552,48 +2546,243 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 36m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>1d 17h 36m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 1:54 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT IN ROUTER</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376615</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra bhulon</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra bhulon</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9818186199</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:00:10 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9818186199</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 11:54:36 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:54:54 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Mitranagar New buspark, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>02:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L33-6</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>1h 54m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -2610,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2647,7 +2836,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2657,7 +2846,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2668,7 +2857,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2869,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>7h 21m</t>
+          <t>6h 34m</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2881,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 56m</t>
+          <t>16h 31m</t>
         </is>
       </c>
     </row>
@@ -2751,14 +2940,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -2896,14 +3085,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -3373,14 +3562,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow inetrnt  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 02:01:16 PM</t>
@@ -3404,6 +3593,73 @@
       <c r="M29" s="5" t="inlineStr">
         <is>
           <t>1d 17h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376615</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra bhulon</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:00:10 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 11:54:36 AM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 01:54:54 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>1h 54m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2h</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2656,10 +2656,8 @@
           <t>Rajendra bhulon</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9818186199</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9818186199</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2745,10 +2743,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2808,7 +2804,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3629,7 +3625,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
     <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2779,6 +2779,213 @@
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 5:35 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376730</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841519997</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:14:20 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841519997</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:09:37 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:35:10 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.720628</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>RB Inn - Hotel Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>awesomeland0132@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB428</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.279862</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>2h 20m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 25m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -2832,7 +3039,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2853,7 +3060,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -2936,14 +3143,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -3081,14 +3288,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_23_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_23_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2851,10 +2851,8 @@
           <t>Binir Kayastha Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841519997</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841519997</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2889,10 +2887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.720628</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.720628</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2944,25 +2940,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB428</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.279862</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.27986199999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
